--- a/02_DIA_inicio_2026_analisis_assets/rbd_9426_escuela-llano-subercaseaux_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9426_escuela-llano-subercaseaux_nt1_rubricas.xlsx
@@ -1920,13 +1920,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF232F3-2A91-4938-8668-9993A0F91381}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E49C5A25-54B2-4C39-A893-AD8BD5B87946}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72C0091B-28CE-4F50-BBED-8FF3C086D864}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{056ED7DA-D332-4A6A-A3D7-E4BD6CC37F57}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A91A7C91-3FDC-47BC-8E7E-849FEBD508CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AD5961E-DD78-453C-A7B1-33B0CF752880}"/>
 </file>